--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_PANATHINAIKOS AKTOR ATHENS.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_PANATHINAIKOS AKTOR ATHENS.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>67.2032</v>
+        <v>49.688</v>
       </c>
       <c r="E2" t="n">
-        <v>41.0139</v>
+        <v>47.189</v>
       </c>
       <c r="F2" t="n">
-        <v>26.1894</v>
+        <v>2.4988</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.8065</v>
+        <v>35.8501</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3261</v>
+        <v>5.992200000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-14.4805</v>
+        <v>29.8585</v>
       </c>
       <c r="J2" t="n">
-        <v>25.6559</v>
+        <v>67.10170000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>25.1925</v>
+        <v>26.4599</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4635000000000002</v>
+        <v>40.6417</v>
       </c>
       <c r="M2" t="n">
-        <v>-41.4618</v>
+        <v>-31.2511</v>
       </c>
       <c r="N2" t="n">
-        <v>-26.5182</v>
+        <v>-20.4679</v>
       </c>
       <c r="O2" t="n">
-        <v>-14.9441</v>
+        <v>-10.783</v>
       </c>
       <c r="P2" t="n">
-        <v>43.8391</v>
+        <v>-1.623399999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-27.6029</v>
+        <v>-58.4526</v>
       </c>
       <c r="R2" t="n">
-        <v>71.4415</v>
+        <v>56.8285</v>
       </c>
       <c r="S2" t="n">
-        <v>45.3212</v>
+        <v>-4.8796</v>
       </c>
       <c r="T2" t="n">
-        <v>27.9981</v>
+        <v>-3.8751</v>
       </c>
       <c r="U2" t="n">
-        <v>17.3229</v>
+        <v>-1.0045</v>
       </c>
       <c r="V2" t="n">
-        <v>-6.1496</v>
+        <v>20.3407</v>
       </c>
       <c r="W2" t="n">
-        <v>14.9623</v>
+        <v>42.4141</v>
       </c>
       <c r="X2" t="n">
-        <v>-21.1119</v>
+        <v>-22.0734</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>31.541</v>
+        <v>39.7813</v>
       </c>
       <c r="E3" t="n">
-        <v>33.896</v>
+        <v>21.8269</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.354900000000001</v>
+        <v>17.9542</v>
       </c>
       <c r="G3" t="n">
-        <v>35.8501</v>
+        <v>-15.8065</v>
       </c>
       <c r="H3" t="n">
-        <v>5.992200000000001</v>
+        <v>-1.3261</v>
       </c>
       <c r="I3" t="n">
-        <v>29.8585</v>
+        <v>-14.4805</v>
       </c>
       <c r="J3" t="n">
-        <v>67.10170000000001</v>
+        <v>25.6559</v>
       </c>
       <c r="K3" t="n">
-        <v>26.4599</v>
+        <v>25.1925</v>
       </c>
       <c r="L3" t="n">
-        <v>40.6417</v>
+        <v>0.4635000000000002</v>
       </c>
       <c r="M3" t="n">
-        <v>-31.2511</v>
+        <v>-41.4618</v>
       </c>
       <c r="N3" t="n">
-        <v>-20.4679</v>
+        <v>-26.5182</v>
       </c>
       <c r="O3" t="n">
-        <v>-10.783</v>
+        <v>-14.9441</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.623399999999999</v>
+        <v>43.8391</v>
       </c>
       <c r="Q3" t="n">
-        <v>-58.4526</v>
+        <v>-27.6029</v>
       </c>
       <c r="R3" t="n">
-        <v>56.8285</v>
+        <v>71.4415</v>
       </c>
       <c r="S3" t="n">
-        <v>-23.0272</v>
+        <v>17.8987</v>
       </c>
       <c r="T3" t="n">
-        <v>-17.1683</v>
+        <v>8.8109</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.8585</v>
+        <v>9.087899999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>20.3407</v>
+        <v>-6.1496</v>
       </c>
       <c r="W3" t="n">
-        <v>42.4141</v>
+        <v>14.9623</v>
       </c>
       <c r="X3" t="n">
-        <v>-22.0734</v>
+        <v>-21.1119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>22.1409</v>
+        <v>39.5889</v>
       </c>
       <c r="E4" t="n">
-        <v>27.1721</v>
+        <v>28.7215</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.0313</v>
+        <v>10.8676</v>
       </c>
       <c r="G4" t="n">
-        <v>2.596800000000001</v>
+        <v>-14.9516</v>
       </c>
       <c r="H4" t="n">
-        <v>10.6217</v>
+        <v>-7.0848</v>
       </c>
       <c r="I4" t="n">
-        <v>-8.024799999999999</v>
+        <v>-7.866699999999998</v>
       </c>
       <c r="J4" t="n">
-        <v>16.1601</v>
+        <v>24.4173</v>
       </c>
       <c r="K4" t="n">
-        <v>13.0681</v>
+        <v>15.4823</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0913</v>
+        <v>8.934699999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-13.5632</v>
+        <v>-39.3689</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4466</v>
+        <v>-22.5669</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.1167</v>
+        <v>-16.8017</v>
       </c>
       <c r="P4" t="n">
-        <v>5.1032</v>
+        <v>34.0972</v>
       </c>
       <c r="Q4" t="n">
-        <v>-18.3246</v>
+        <v>-33.6336</v>
       </c>
       <c r="R4" t="n">
-        <v>23.4275</v>
+        <v>67.73009999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>19.0931</v>
+        <v>-5.0365</v>
       </c>
       <c r="T4" t="n">
-        <v>17.4181</v>
+        <v>-7.3923</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6751</v>
+        <v>2.3559</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.652</v>
+        <v>25.4803</v>
       </c>
       <c r="W4" t="n">
-        <v>11.9185</v>
+        <v>45.3297</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.5705</v>
+        <v>-19.8494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>18.4923</v>
+        <v>27.1354</v>
       </c>
       <c r="E5" t="n">
-        <v>16.5528</v>
+        <v>17.5166</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9395</v>
+        <v>9.618599999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>6.097899999999999</v>
+        <v>14.3894</v>
       </c>
       <c r="H5" t="n">
-        <v>4.079400000000001</v>
+        <v>3.0386</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0191</v>
+        <v>11.351</v>
       </c>
       <c r="J5" t="n">
-        <v>13.8273</v>
+        <v>52.5446</v>
       </c>
       <c r="K5" t="n">
-        <v>9.3371</v>
+        <v>25.9713</v>
       </c>
       <c r="L5" t="n">
-        <v>4.4901</v>
+        <v>26.5738</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.7291</v>
+        <v>-38.1554</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.2577</v>
+        <v>-22.9328</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4712</v>
+        <v>-15.2228</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4637000000000002</v>
+        <v>20.6441</v>
       </c>
       <c r="Q5" t="n">
-        <v>-17.8606</v>
+        <v>-45.6951</v>
       </c>
       <c r="R5" t="n">
-        <v>17.3968</v>
+        <v>66.3386</v>
       </c>
       <c r="S5" t="n">
-        <v>13.4254</v>
+        <v>-10.6268</v>
       </c>
       <c r="T5" t="n">
-        <v>9.5494</v>
+        <v>-6.6932</v>
       </c>
       <c r="U5" t="n">
-        <v>3.8759</v>
+        <v>-3.934</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5671000000000004</v>
+        <v>2.729</v>
       </c>
       <c r="W5" t="n">
-        <v>11.0367</v>
+        <v>17.3592</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.6038</v>
+        <v>-14.6302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>16.6983</v>
+        <v>9.533700000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>10.8834</v>
+        <v>14.0126</v>
       </c>
       <c r="F6" t="n">
-        <v>5.815</v>
+        <v>-4.4789</v>
       </c>
       <c r="G6" t="n">
-        <v>-14.9516</v>
+        <v>2.596800000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.0848</v>
+        <v>10.6217</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.866699999999998</v>
+        <v>-8.024799999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>24.4173</v>
+        <v>16.1601</v>
       </c>
       <c r="K6" t="n">
-        <v>15.4823</v>
+        <v>13.0681</v>
       </c>
       <c r="L6" t="n">
-        <v>8.934699999999999</v>
+        <v>3.0913</v>
       </c>
       <c r="M6" t="n">
-        <v>-39.3689</v>
+        <v>-13.5632</v>
       </c>
       <c r="N6" t="n">
-        <v>-22.5669</v>
+        <v>-2.4466</v>
       </c>
       <c r="O6" t="n">
-        <v>-16.8017</v>
+        <v>-11.1167</v>
       </c>
       <c r="P6" t="n">
-        <v>34.0972</v>
+        <v>5.1032</v>
       </c>
       <c r="Q6" t="n">
-        <v>-33.6336</v>
+        <v>-18.3246</v>
       </c>
       <c r="R6" t="n">
-        <v>67.73009999999999</v>
+        <v>23.4275</v>
       </c>
       <c r="S6" t="n">
-        <v>-27.9272</v>
+        <v>6.486</v>
       </c>
       <c r="T6" t="n">
-        <v>-25.2301</v>
+        <v>4.2585</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.697</v>
+        <v>2.2277</v>
       </c>
       <c r="V6" t="n">
-        <v>25.4803</v>
+        <v>-4.652</v>
       </c>
       <c r="W6" t="n">
-        <v>45.3297</v>
+        <v>11.9185</v>
       </c>
       <c r="X6" t="n">
-        <v>-19.8494</v>
+        <v>-16.5705</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>9.3757</v>
+        <v>9.2164</v>
       </c>
       <c r="E7" t="n">
-        <v>13.404</v>
+        <v>11.6976</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.0285</v>
+        <v>-2.4812</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5384</v>
@@ -1000,13 +1000,13 @@
         <v>19.0202</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1862</v>
+        <v>-0.3455999999999998</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7467</v>
+        <v>-0.9597</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9329999999999999</v>
+        <v>0.6142999999999998</v>
       </c>
       <c r="V7" t="n">
         <v>1.7501</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>3.276800000000001</v>
+        <v>8.3566</v>
       </c>
       <c r="E8" t="n">
-        <v>4.632599999999998</v>
+        <v>8.241199999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3558</v>
+        <v>0.1153999999999997</v>
       </c>
       <c r="G8" t="n">
-        <v>14.3894</v>
+        <v>6.097899999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0386</v>
+        <v>4.079400000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>11.351</v>
+        <v>2.0191</v>
       </c>
       <c r="J8" t="n">
-        <v>52.5446</v>
+        <v>13.8273</v>
       </c>
       <c r="K8" t="n">
-        <v>25.9713</v>
+        <v>9.3371</v>
       </c>
       <c r="L8" t="n">
-        <v>26.5738</v>
+        <v>4.4901</v>
       </c>
       <c r="M8" t="n">
-        <v>-38.1554</v>
+        <v>-7.7291</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.9328</v>
+        <v>-5.2577</v>
       </c>
       <c r="O8" t="n">
-        <v>-15.2228</v>
+        <v>-2.4712</v>
       </c>
       <c r="P8" t="n">
-        <v>20.6441</v>
+        <v>-0.4637000000000002</v>
       </c>
       <c r="Q8" t="n">
-        <v>-45.6951</v>
+        <v>-17.8606</v>
       </c>
       <c r="R8" t="n">
-        <v>66.3386</v>
+        <v>17.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>-34.4851</v>
+        <v>3.2892</v>
       </c>
       <c r="T8" t="n">
-        <v>-19.5772</v>
+        <v>1.2376</v>
       </c>
       <c r="U8" t="n">
-        <v>-14.9081</v>
+        <v>2.0518</v>
       </c>
       <c r="V8" t="n">
-        <v>2.729</v>
+        <v>-0.5671000000000004</v>
       </c>
       <c r="W8" t="n">
-        <v>17.3592</v>
+        <v>11.0367</v>
       </c>
       <c r="X8" t="n">
-        <v>-14.6302</v>
+        <v>-11.6038</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>V. TOLIOPOULOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>2.792</v>
+        <v>7.5801</v>
       </c>
       <c r="E9" t="n">
-        <v>7.1701</v>
+        <v>4.290900000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.3781</v>
+        <v>3.2894</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5515000000000008</v>
+        <v>-1.972100000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.0088</v>
+        <v>-1.7009</v>
       </c>
       <c r="I9" t="n">
-        <v>3.457</v>
+        <v>-0.2713000000000003</v>
       </c>
       <c r="J9" t="n">
-        <v>9.991099999999999</v>
+        <v>1.8696</v>
       </c>
       <c r="K9" t="n">
-        <v>4.764699999999999</v>
+        <v>-0.9333999999999998</v>
       </c>
       <c r="L9" t="n">
-        <v>5.2263</v>
+        <v>2.8029</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.5426</v>
+        <v>-3.8416</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.7735</v>
+        <v>-0.7672</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7692</v>
+        <v>-3.0743</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.479299999999999</v>
+        <v>6.262799999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-15.3089</v>
+        <v>-1.6237</v>
       </c>
       <c r="R9" t="n">
-        <v>11.8297</v>
+        <v>7.8865</v>
       </c>
       <c r="S9" t="n">
-        <v>11.5855</v>
+        <v>1.1452</v>
       </c>
       <c r="T9" t="n">
-        <v>7.9953</v>
+        <v>0.2923</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5906</v>
+        <v>0.8529</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.7627</v>
+        <v>2.1444</v>
       </c>
       <c r="W9" t="n">
-        <v>4.4928</v>
+        <v>3.7527</v>
       </c>
       <c r="X9" t="n">
-        <v>-9.2555</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>2.017300000000001</v>
+        <v>2.668299999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3137</v>
+        <v>0.1461999999999992</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3308</v>
+        <v>2.5218</v>
       </c>
       <c r="G10" t="n">
         <v>-8.258099999999999</v>
@@ -1234,13 +1234,13 @@
         <v>26.443</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1447999999999999</v>
+        <v>0.7955</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9047999999999999</v>
+        <v>1.3647</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7604</v>
+        <v>-0.5694999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-4.714200000000001</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. TOLIOPOULOS</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0038</v>
+        <v>1.758399999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4587</v>
+        <v>-5.750200000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4625</v>
+        <v>7.5085</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.972100000000001</v>
+        <v>2.6812</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7009</v>
+        <v>-4.202500000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2713000000000003</v>
+        <v>6.8836</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8696</v>
+        <v>29.9357</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9333999999999998</v>
+        <v>10.8425</v>
       </c>
       <c r="L11" t="n">
-        <v>2.8029</v>
+        <v>19.0937</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.8416</v>
+        <v>-27.2543</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7672</v>
+        <v>-15.0446</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.0743</v>
+        <v>-12.2099</v>
       </c>
       <c r="P11" t="n">
-        <v>6.262799999999999</v>
+        <v>-6.494499999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.6237</v>
+        <v>-50.102</v>
       </c>
       <c r="R11" t="n">
-        <v>7.8865</v>
+        <v>43.6076</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.431</v>
+        <v>-4.7694</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.457100000000001</v>
+        <v>-5.8898</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.974</v>
+        <v>1.1206</v>
       </c>
       <c r="V11" t="n">
-        <v>2.1444</v>
+        <v>10.3414</v>
       </c>
       <c r="W11" t="n">
-        <v>3.7527</v>
+        <v>20.3058</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6083</v>
+        <v>-9.964500000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>A. SAMODUROV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1286000000000003</v>
+        <v>0.8602000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>18.6312</v>
+        <v>0.7049000000000007</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.7604</v>
+        <v>0.1553</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.3216</v>
+        <v>0.9756000000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>1.190299999999999</v>
+        <v>3.1542</v>
       </c>
       <c r="I12" t="n">
-        <v>-12.5118</v>
+        <v>-2.1783</v>
       </c>
       <c r="J12" t="n">
-        <v>13.7771</v>
+        <v>4.8657</v>
       </c>
       <c r="K12" t="n">
-        <v>10.3309</v>
+        <v>6.1876</v>
       </c>
       <c r="L12" t="n">
-        <v>3.4459</v>
+        <v>-1.3219</v>
       </c>
       <c r="M12" t="n">
-        <v>-25.0986</v>
+        <v>-3.8899</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.140600000000001</v>
+        <v>-3.0336</v>
       </c>
       <c r="O12" t="n">
-        <v>-15.958</v>
+        <v>-0.8562000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-12.0617</v>
+        <v>2.3196</v>
       </c>
       <c r="Q12" t="n">
-        <v>-38.5045</v>
+        <v>-3.9433</v>
       </c>
       <c r="R12" t="n">
-        <v>26.4431</v>
+        <v>6.2629</v>
       </c>
       <c r="S12" t="n">
-        <v>35.7749</v>
+        <v>-0.4325</v>
       </c>
       <c r="T12" t="n">
-        <v>31.0145</v>
+        <v>-0.8955</v>
       </c>
       <c r="U12" t="n">
-        <v>4.7604</v>
+        <v>0.463</v>
       </c>
       <c r="V12" t="n">
-        <v>-12.5208</v>
+        <v>-2.0026</v>
       </c>
       <c r="W12" t="n">
-        <v>12.3438</v>
+        <v>0.6779000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-24.8646</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SAMODUROV</t>
+          <t>I. KOUZELOGLOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4584999999999997</v>
+        <v>-2.7065</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1270000000000002</v>
+        <v>-3.1979</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5854000000000001</v>
+        <v>0.4914000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9756000000000002</v>
+        <v>-0.1887000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1542</v>
+        <v>-1.0454</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1783</v>
+        <v>0.8567</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8657</v>
+        <v>0.4265</v>
       </c>
       <c r="K13" t="n">
-        <v>6.1876</v>
+        <v>0.3529</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3219</v>
+        <v>0.0736</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.8899</v>
+        <v>-0.6152</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.0336</v>
+        <v>-1.3982</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8562000000000001</v>
+        <v>0.7831000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3196</v>
+        <v>-2.5516</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9433</v>
+        <v>-3.4794</v>
       </c>
       <c r="R13" t="n">
-        <v>6.2629</v>
+        <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.751</v>
+        <v>-0.3607</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4734</v>
+        <v>-0.1453</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2777000000000001</v>
+        <v>-0.2155</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0026</v>
+        <v>0.3943</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6779000000000001</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.6805</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. KOUZELOGLOU</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.877</v>
+        <v>-5.4805</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.1547</v>
+        <v>0.5215999999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2776999999999999</v>
+        <v>-6.002</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1887000000000001</v>
+        <v>-0.5515000000000008</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0454</v>
+        <v>-4.0088</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8567</v>
+        <v>3.457</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4265</v>
+        <v>9.991099999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3529</v>
+        <v>4.764699999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0736</v>
+        <v>5.2263</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6152</v>
+        <v>-10.5426</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3982</v>
+        <v>-8.7735</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7831000000000001</v>
+        <v>-1.7692</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.5516</v>
+        <v>-3.479299999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.4794</v>
+        <v>-15.3089</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>11.8297</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5311000000000001</v>
+        <v>3.3131</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1019</v>
+        <v>1.3467</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4292</v>
+        <v>1.9665</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3943</v>
+        <v>-4.7627</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.4928</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3943</v>
+        <v>-9.2555</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.3005</v>
+        <v>-7.6562</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.0068</v>
+        <v>-4.1501</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7057999999999991</v>
+        <v>-3.5059</v>
       </c>
       <c r="G15" t="n">
-        <v>-20.4499</v>
+        <v>-4.9146</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.5158</v>
+        <v>1.4557</v>
       </c>
       <c r="I15" t="n">
-        <v>-9.934000000000001</v>
+        <v>-6.3706</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.8676</v>
+        <v>2.7414</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5744</v>
+        <v>4.7158</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.4419</v>
+        <v>-1.9746</v>
       </c>
       <c r="M15" t="n">
-        <v>-17.5822</v>
+        <v>-7.6558</v>
       </c>
       <c r="N15" t="n">
-        <v>-12.0898</v>
+        <v>-3.2601</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.492299999999999</v>
+        <v>-4.395799999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>8.3505</v>
+        <v>6.494899999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-22.9636</v>
+        <v>-5.567</v>
       </c>
       <c r="R15" t="n">
-        <v>31.314</v>
+        <v>12.062</v>
       </c>
       <c r="S15" t="n">
-        <v>6.7245</v>
+        <v>-1.4469</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2514</v>
+        <v>-1.072</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4729</v>
+        <v>-0.3751</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.9256</v>
+        <v>-7.789</v>
       </c>
       <c r="W15" t="n">
-        <v>11.5728</v>
+        <v>-0.2524999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-15.4984</v>
+        <v>-7.5365</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.1046</v>
+        <v>-10.6662</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.261299999999999</v>
+        <v>-3.7117</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.8433</v>
+        <v>-6.9544</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.9146</v>
+        <v>-6.1655</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4557</v>
+        <v>-2.8994</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.3706</v>
+        <v>-3.2655</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7414</v>
+        <v>-0.8863</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7158</v>
+        <v>-0.5812999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.9746</v>
+        <v>-0.3048999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.6558</v>
+        <v>-5.2792</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.2601</v>
+        <v>-2.3181</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.395799999999999</v>
+        <v>-2.9606</v>
       </c>
       <c r="P16" t="n">
-        <v>6.494899999999999</v>
+        <v>0.2322000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.567</v>
+        <v>-3.0155</v>
       </c>
       <c r="R16" t="n">
-        <v>12.062</v>
+        <v>3.2477</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.8955</v>
+        <v>0.3757</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.1831</v>
+        <v>0.1898</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7127</v>
+        <v>0.1859000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-7.789</v>
+        <v>-5.1085</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.2524999999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.5365</v>
+        <v>-5.1085</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.7123</v>
+        <v>-14.0635</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.861000000000001</v>
+        <v>-4.058199999999998</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.8512</v>
+        <v>-10.0048</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.1655</v>
+        <v>22.8756</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.8994</v>
+        <v>17.443</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.2655</v>
+        <v>5.432500000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8863</v>
+        <v>68.4205</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5812999999999999</v>
+        <v>44.9716</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3048999999999999</v>
+        <v>23.4491</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.2792</v>
+        <v>-45.5451</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.3181</v>
+        <v>-27.5284</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.9606</v>
+        <v>-18.0162</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2322000000000001</v>
+        <v>-42.6792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0155</v>
+        <v>-108.7851</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2477</v>
+        <v>66.10679999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6706000000000001</v>
+        <v>-2.886400000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.04060000000000002</v>
+        <v>-4.1056</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7107</v>
+        <v>1.2192</v>
       </c>
       <c r="V17" t="n">
-        <v>-5.1085</v>
+        <v>8.625999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>40.4114</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.1085</v>
+        <v>-31.7854</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.0945</v>
+        <v>-14.8325</v>
       </c>
       <c r="E18" t="n">
-        <v>-21.1859</v>
+        <v>-14.2331</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0914</v>
+        <v>-0.5992999999999997</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6812</v>
+        <v>-20.4499</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.202500000000001</v>
+        <v>-10.5158</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8836</v>
+        <v>-9.934000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>29.9357</v>
+        <v>-2.8676</v>
       </c>
       <c r="K18" t="n">
-        <v>10.8425</v>
+        <v>1.5744</v>
       </c>
       <c r="L18" t="n">
-        <v>19.0937</v>
+        <v>-4.4419</v>
       </c>
       <c r="M18" t="n">
-        <v>-27.2543</v>
+        <v>-17.5822</v>
       </c>
       <c r="N18" t="n">
-        <v>-15.0446</v>
+        <v>-12.0898</v>
       </c>
       <c r="O18" t="n">
-        <v>-12.2099</v>
+        <v>-5.492299999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.494499999999999</v>
+        <v>8.3505</v>
       </c>
       <c r="Q18" t="n">
-        <v>-50.102</v>
+        <v>-22.9636</v>
       </c>
       <c r="R18" t="n">
-        <v>43.6076</v>
+        <v>31.314</v>
       </c>
       <c r="S18" t="n">
-        <v>-25.6219</v>
+        <v>1.1922</v>
       </c>
       <c r="T18" t="n">
-        <v>-21.3255</v>
+        <v>0.02470000000000022</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.2964</v>
+        <v>1.1675</v>
       </c>
       <c r="V18" t="n">
-        <v>10.3414</v>
+        <v>-3.9256</v>
       </c>
       <c r="W18" t="n">
-        <v>20.3058</v>
+        <v>11.5728</v>
       </c>
       <c r="X18" t="n">
-        <v>-9.964500000000001</v>
+        <v>-15.4984</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>-38.72320000000001</v>
+        <v>-23.2659</v>
       </c>
       <c r="E19" t="n">
-        <v>-21.0588</v>
+        <v>-2.313000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-17.6641</v>
+        <v>-20.9528</v>
       </c>
       <c r="G19" t="n">
-        <v>22.8756</v>
+        <v>-11.3216</v>
       </c>
       <c r="H19" t="n">
-        <v>17.443</v>
+        <v>1.190299999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>5.432500000000001</v>
+        <v>-12.5118</v>
       </c>
       <c r="J19" t="n">
-        <v>68.4205</v>
+        <v>13.7771</v>
       </c>
       <c r="K19" t="n">
-        <v>44.9716</v>
+        <v>10.3309</v>
       </c>
       <c r="L19" t="n">
-        <v>23.4491</v>
+        <v>3.4459</v>
       </c>
       <c r="M19" t="n">
-        <v>-45.5451</v>
+        <v>-25.0986</v>
       </c>
       <c r="N19" t="n">
-        <v>-27.5284</v>
+        <v>-9.140600000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-18.0162</v>
+        <v>-15.958</v>
       </c>
       <c r="P19" t="n">
-        <v>-42.6792</v>
+        <v>-12.0617</v>
       </c>
       <c r="Q19" t="n">
-        <v>-108.7851</v>
+        <v>-38.5045</v>
       </c>
       <c r="R19" t="n">
-        <v>66.10679999999999</v>
+        <v>26.4431</v>
       </c>
       <c r="S19" t="n">
-        <v>-27.5461</v>
+        <v>12.6377</v>
       </c>
       <c r="T19" t="n">
-        <v>-21.1059</v>
+        <v>10.0701</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.440300000000001</v>
+        <v>2.5678</v>
       </c>
       <c r="V19" t="n">
-        <v>8.625999999999999</v>
+        <v>-12.5208</v>
       </c>
       <c r="W19" t="n">
-        <v>40.4114</v>
+        <v>12.3438</v>
       </c>
       <c r="X19" t="n">
-        <v>-31.7854</v>
+        <v>-24.8646</v>
       </c>
     </row>
     <row r="20">
@@ -1969,25 +1969,25 @@
         <v>38</v>
       </c>
       <c r="D20" t="n">
-        <v>82.1421</v>
+        <v>117.496</v>
       </c>
       <c r="E20" t="n">
-        <v>107.1822</v>
+        <v>117.4548</v>
       </c>
       <c r="F20" t="n">
-        <v>-25.0409</v>
+        <v>0.04169999999999874</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3481000000000165</v>
+        <v>0.348100000000013</v>
       </c>
       <c r="H20" t="n">
         <v>14.2097</v>
       </c>
       <c r="I20" t="n">
-        <v>-13.85939999999999</v>
+        <v>-13.8594</v>
       </c>
       <c r="J20" t="n">
-        <v>340.8589</v>
+        <v>340.8589000000001</v>
       </c>
       <c r="K20" t="n">
         <v>209.1068</v>
@@ -2005,7 +2005,7 @@
         <v>-145.6113</v>
       </c>
       <c r="P20" t="n">
-        <v>81.1858</v>
+        <v>81.18579999999999</v>
       </c>
       <c r="Q20" t="n">
         <v>-477.1302</v>
@@ -2014,16 +2014,16 @@
         <v>558.3143</v>
       </c>
       <c r="S20" t="n">
-        <v>-19.00350000000001</v>
+        <v>16.3489</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.70360000000002</v>
+        <v>-3.433199999999998</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.3002</v>
+        <v>19.7824</v>
       </c>
       <c r="V20" t="n">
-        <v>19.6141</v>
+        <v>19.61409999999999</v>
       </c>
       <c r="W20" t="n">
         <v>257.1535</v>
